--- a/docs/templates/PnL_Cashflow_Template_Monthly.xlsx
+++ b/docs/templates/PnL_Cashflow_Template_Monthly.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="46">
   <si>
     <t xml:space="preserve">Cara guna template ini</t>
   </si>
@@ -30,34 +30,40 @@
     <t xml:space="preserve">1. Ada 2 tab: 'PnL' dan 'Cashflow'. Isi tab yang berkaitan.</t>
   </si>
   <si>
-    <t xml:space="preserve">2. JANGAN merge cell pada column Type — taip value (cth 'Cash-Out') pada SETIAP baris walaupun berulang.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Jangan tukar nama header (Type, Category, Total) atau susunan column.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Isi angka bulanan sahaja — column Total auto-kira, jangan edit terus.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Untuk expense/Cash-Out, taip nombor POSITIF — app auto-tolak (negative) bila import berdasarkan Type.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. Tukar label bulan (Jan, Feb...) di baris 5 jika perlu label tahun khusus, cth 'Jan-26'.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7. Padam baris contoh (bergaris kuning) sebelum isi data sebenar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8. Bila upload dalam app, pilih statement type (PnL/Cashflow) yang sepadan dengan tab yang diisi.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PnL Template — isi bermula dari baris 5. JANGAN merge cell, JANGAN tukar nama header (Type, Category, Total).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type = kumpulan (cth: Revenue/COGS/Opex untuk PnL, atau Cash-In/Cash-Out untuk Cashflow) — TAIP pada SETIAP baris, jangan biarkan kosong walaupun sama dengan baris atas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isi angka bulanan (column D-O). Column 'Total' auto-kira (formula) — jangan taip manual. Untuk Cash-Out/expense, taip nombor POSITIF sahaja (app akan tolak secara automatik ikut Type).</t>
+    <t xml:space="preserve">2. Category/Type dan Subcategory dalam template ni SAMA dengan yang app PROFIT guna — jangan tukar nama, supaya data automatik disusun betul.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Senarai Subcategory (Cost) standard: Direct Manpower, Project Allowance, Travel &amp; Accommodations, Vehicle Leasing / Cost, Equipment &amp; Hardware, Permit &amp; Regulatory, Other Direct Project Cost, Salary, Shared Service.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Boleh tambah Subcategory baru kalau perlu — app akan terima category/subcategory baru secara automatik.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. JANGAN merge cell pada column Type/Category — taip value pada SETIAP baris walaupun berulang.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Isi angka bulanan sahaja — column Total auto-kira, jangan edit terus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. Untuk expense/Cash-Out, taip nombor POSITIF — app auto-tolak (negative) bila import berdasarkan Type.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. Tukar label bulan (Jan, Feb...) di baris 5 jika perlu label tahun khusus, cth 'Jan-26'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. Padam baris contoh (bergaris hijau) sebelum isi data sebenar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bila upload dalam app, pilih statement type (PnL/Cashflow) yang sepadan dengan tab yang diisi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PnL Template (Monthly) — isi bermula dari baris 5. JANGAN merge cell, JANGAN tukar nama header (Type, Category, Total).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type = 'Revenue' atau 'Expenses' — TAIP pada SETIAP baris (jangan biarkan kosong walaupun sama dengan baris atas). Category = item spesifik (contoh: Direct Manpower).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isi angka bulanan (column C-N). Column 'Total' auto-kira (formula). Untuk Expenses/expense, taip nombor POSITIF sahaja — app auto-tolak (jadi negatif) secara automatik ikut Type.</t>
   </si>
   <si>
     <t xml:space="preserve">Type</t>
@@ -108,34 +114,52 @@
     <t xml:space="preserve">Revenue</t>
   </si>
   <si>
-    <t xml:space="preserve">Project Billing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COGS</t>
+    <t xml:space="preserve">Client Payment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expenses</t>
   </si>
   <si>
     <t xml:space="preserve">Direct Manpower</t>
   </si>
   <si>
-    <t xml:space="preserve">Opex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software &amp; Licenses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cashflow Template — isi bermula dari baris 5. JANGAN merge cell, JANGAN tukar nama header (Type, Category, Total).</t>
+    <t xml:space="preserve">Project Allowance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travel &amp; Accommodations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle Leasing / Cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equipment &amp; Hardware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Permit &amp; Regulatory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other Direct Project Cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shared Service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cashflow Template (Monthly) — isi bermula dari baris 5. JANGAN merge cell, JANGAN tukar nama header (Type, Category, Total).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type = 'Cash-In' atau 'Cash-Out' — TAIP pada SETIAP baris (jangan biarkan kosong walaupun sama dengan baris atas). Category = item spesifik (contoh: Direct Manpower).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isi angka bulanan (column C-N). Column 'Total' auto-kira (formula). Untuk Cash-Out/expense, taip nombor POSITIF sahaja — app auto-tolak (jadi negatif) secara automatik ikut Type.</t>
   </si>
   <si>
     <t xml:space="preserve">Cash-In</t>
   </si>
   <si>
-    <t xml:space="preserve">Client Payment</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cash-Out</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vehicle Cost</t>
   </si>
 </sst>
 </file>
@@ -172,14 +196,14 @@
     <font>
       <b val="true"/>
       <sz val="14"/>
-      <color rgb="FF1C2321"/>
+      <color rgb="FF101A2C"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1C2321"/>
+      <color rgb="FF101A2C"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -187,7 +211,7 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color rgb="FF1C2321"/>
+      <color rgb="FF101A2C"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -195,7 +219,7 @@
     <font>
       <i val="true"/>
       <sz val="10"/>
-      <color rgb="FF8A8578"/>
+      <color rgb="FF6B6A63"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -203,7 +227,7 @@
     <font>
       <b val="true"/>
       <sz val="10.5"/>
-      <color rgb="FFF7F5F0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -211,7 +235,7 @@
     <font>
       <i val="true"/>
       <sz val="10.5"/>
-      <color rgb="FF7A5E14"/>
+      <color rgb="FF2F8F86"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -239,14 +263,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1C2321"/>
-        <bgColor rgb="FF333300"/>
+        <fgColor rgb="FF101A2C"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF9E5"/>
-        <bgColor rgb="FFF7F5F0"/>
+        <fgColor rgb="FFE4F1EF"/>
+        <bgColor rgb="FFCCFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -260,16 +284,16 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
-        <color rgb="FFD8D3C6"/>
+        <color rgb="FFDCD8CB"/>
       </left>
       <right style="thin">
-        <color rgb="FFD8D3C6"/>
+        <color rgb="FFDCD8CB"/>
       </right>
       <top style="thin">
-        <color rgb="FFD8D3C6"/>
+        <color rgb="FFDCD8CB"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFD8D3C6"/>
+        <color rgb="FFDCD8CB"/>
       </bottom>
       <diagonal/>
     </border>
@@ -299,7 +323,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -340,11 +364,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -360,7 +388,7 @@
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFF7F5F0"/>
+      <rgbColor rgb="FFFFFFFF"/>
       <rgbColor rgb="FFFF0000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
@@ -370,19 +398,19 @@
       <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF7A5E14"/>
+      <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFD8D3C6"/>
-      <rgbColor rgb="FF8A8578"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF9E5"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFE4F1EF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFDCD8CB"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -405,16 +433,16 @@
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF6B6A63"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF2F8F86"/>
+      <rgbColor rgb="FF101A2C"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF1C2321"/>
+      <rgbColor rgb="FF333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -600,7 +628,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="95"/>
@@ -624,12 +652,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -644,7 +672,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -652,6 +680,19 @@
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -670,7 +711,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
@@ -681,7 +722,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -689,9 +730,9 @@
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -709,7 +750,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -727,57 +768,57 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C6" s="8" t="n">
         <v>150000</v>
@@ -786,10 +827,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>120000</v>
+        <v>0</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="G6" s="8" t="n">
         <v>0</v>
@@ -817,55 +858,55 @@
       </c>
       <c r="O6" s="8" t="n">
         <f aca="false">SUM(C6:N6)</f>
-        <v>270000</v>
+        <v>330000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>45000</v>
+        <v>21541</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>45000</v>
+        <v>21541</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>45000</v>
+        <v>21541</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>45000</v>
+        <v>21541</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>45000</v>
+        <v>21541</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>45000</v>
+        <v>21541</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>45000</v>
+        <v>21541</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>45000</v>
+        <v>21541</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>45000</v>
+        <v>21541</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>45000</v>
+        <v>21541</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>45000</v>
+        <v>21541</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>45000</v>
+        <v>21541</v>
       </c>
       <c r="O7" s="8" t="n">
         <f aca="false">SUM(C7:N7)</f>
-        <v>540000</v>
+        <v>258492</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -873,7 +914,7 @@
         <v>31</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>3200</v>
@@ -917,28 +958,60 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="11" t="n">
+      <c r="A9" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J9" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="K9" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L9" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="M9" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="N9" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="O9" s="8" t="n">
         <f aca="false">SUM(C9:N9)</f>
-        <v>0</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
+      <c r="A10" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>35</v>
+      </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
       <c r="E10" s="10"/>
@@ -957,8 +1030,12 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
+      <c r="A11" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
@@ -977,8 +1054,12 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
+      <c r="A12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>37</v>
+      </c>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -997,8 +1078,12 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
+      <c r="A13" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>38</v>
+      </c>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
@@ -1017,8 +1102,12 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
+      <c r="A14" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
@@ -1037,8 +1126,12 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
+      <c r="A15" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>40</v>
+      </c>
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
@@ -1059,18 +1152,18 @@
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9"/>
       <c r="B16" s="9"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
       <c r="O16" s="11" t="n">
         <f aca="false">SUM(C16:N16)</f>
         <v>0</v>
@@ -1079,18 +1172,18 @@
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
       <c r="O17" s="11" t="n">
         <f aca="false">SUM(C17:N17)</f>
         <v>0</v>
@@ -1099,18 +1192,18 @@
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
       <c r="O18" s="11" t="n">
         <f aca="false">SUM(C18:N18)</f>
         <v>0</v>
@@ -1119,18 +1212,18 @@
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
       <c r="O19" s="11" t="n">
         <f aca="false">SUM(C19:N19)</f>
         <v>0</v>
@@ -1139,18 +1232,18 @@
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
       <c r="O20" s="11" t="n">
         <f aca="false">SUM(C20:N20)</f>
         <v>0</v>
@@ -1159,120 +1252,20 @@
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9"/>
       <c r="B21" s="9"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="12"/>
       <c r="O21" s="11" t="n">
         <f aca="false">SUM(C21:N21)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="10"/>
-      <c r="O22" s="11" t="n">
-        <f aca="false">SUM(C22:N22)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
-      <c r="O23" s="11" t="n">
-        <f aca="false">SUM(C23:N23)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
-      <c r="O24" s="11" t="n">
-        <f aca="false">SUM(C24:N24)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="11" t="n">
-        <f aca="false">SUM(C25:N25)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="10"/>
-      <c r="N26" s="10"/>
-      <c r="O26" s="11" t="n">
-        <f aca="false">SUM(C26:N26)</f>
         <v>0</v>
       </c>
     </row>
@@ -1297,7 +1290,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
@@ -1308,7 +1301,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -1316,9 +1309,9 @@
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -1336,7 +1329,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -1354,57 +1347,57 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C6" s="8" t="n">
         <v>150000</v>
@@ -1413,10 +1406,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>120000</v>
+        <v>0</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="G6" s="8" t="n">
         <v>0</v>
@@ -1444,128 +1437,160 @@
       </c>
       <c r="O6" s="8" t="n">
         <f aca="false">SUM(C6:N6)</f>
-        <v>270000</v>
+        <v>330000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>45000</v>
+        <v>21541</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>45000</v>
+        <v>21541</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>45000</v>
+        <v>21541</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>45000</v>
+        <v>21541</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>45000</v>
+        <v>21541</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>45000</v>
+        <v>21541</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>45000</v>
+        <v>21541</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>45000</v>
+        <v>21541</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>45000</v>
+        <v>21541</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>45000</v>
+        <v>21541</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>45000</v>
+        <v>21541</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>45000</v>
+        <v>21541</v>
       </c>
       <c r="O7" s="8" t="n">
         <f aca="false">SUM(C7:N7)</f>
-        <v>540000</v>
+        <v>258492</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>2350.6</v>
+        <v>3200</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>2350.6</v>
+        <v>3200</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>2350.6</v>
+        <v>3200</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>2350.6</v>
+        <v>3200</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>2350.6</v>
+        <v>3200</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>2350.6</v>
+        <v>3200</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>2350.6</v>
+        <v>3200</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>2350.6</v>
+        <v>3200</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>2350.6</v>
+        <v>3200</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>2350.6</v>
+        <v>3200</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>2350.6</v>
+        <v>3200</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>2350.6</v>
+        <v>3200</v>
       </c>
       <c r="O8" s="8" t="n">
         <f aca="false">SUM(C8:N8)</f>
-        <v>28207.2</v>
+        <v>38400</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="11" t="n">
+      <c r="A9" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J9" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="K9" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L9" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="M9" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="N9" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="O9" s="8" t="n">
         <f aca="false">SUM(C9:N9)</f>
-        <v>0</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
+      <c r="A10" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>35</v>
+      </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
       <c r="E10" s="10"/>
@@ -1584,8 +1609,12 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
+      <c r="A11" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
@@ -1604,8 +1633,12 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
+      <c r="A12" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>37</v>
+      </c>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -1624,8 +1657,12 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
+      <c r="A13" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>38</v>
+      </c>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
@@ -1644,8 +1681,12 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
+      <c r="A14" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
@@ -1664,8 +1705,12 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
+      <c r="A15" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>40</v>
+      </c>
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
@@ -1686,18 +1731,18 @@
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9"/>
       <c r="B16" s="9"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
       <c r="O16" s="11" t="n">
         <f aca="false">SUM(C16:N16)</f>
         <v>0</v>
@@ -1706,18 +1751,18 @@
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
       <c r="O17" s="11" t="n">
         <f aca="false">SUM(C17:N17)</f>
         <v>0</v>
@@ -1726,18 +1771,18 @@
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
       <c r="O18" s="11" t="n">
         <f aca="false">SUM(C18:N18)</f>
         <v>0</v>
@@ -1746,18 +1791,18 @@
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
       <c r="O19" s="11" t="n">
         <f aca="false">SUM(C19:N19)</f>
         <v>0</v>
@@ -1766,18 +1811,18 @@
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
       <c r="O20" s="11" t="n">
         <f aca="false">SUM(C20:N20)</f>
         <v>0</v>
@@ -1786,120 +1831,20 @@
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9"/>
       <c r="B21" s="9"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="12"/>
       <c r="O21" s="11" t="n">
         <f aca="false">SUM(C21:N21)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="10"/>
-      <c r="O22" s="11" t="n">
-        <f aca="false">SUM(C22:N22)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
-      <c r="O23" s="11" t="n">
-        <f aca="false">SUM(C23:N23)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
-      <c r="O24" s="11" t="n">
-        <f aca="false">SUM(C24:N24)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="11" t="n">
-        <f aca="false">SUM(C25:N25)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="10"/>
-      <c r="N26" s="10"/>
-      <c r="O26" s="11" t="n">
-        <f aca="false">SUM(C26:N26)</f>
         <v>0</v>
       </c>
     </row>

--- a/docs/templates/PnL_Cashflow_Template_Monthly.xlsx
+++ b/docs/templates/PnL_Cashflow_Template_Monthly.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Cara Guna" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="How To Use" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="PnL" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Cashflow" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
@@ -24,49 +24,49 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="47">
   <si>
-    <t xml:space="preserve">Cara guna template ini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Ada 2 tab: 'PnL' dan 'Cashflow'. Isi tab yang berkaitan.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Category/Type dan Subcategory dalam template ni SAMA dengan yang app PROFIT guna — jangan tukar nama, supaya data automatik disusun betul.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Senarai Subcategory (Cost) standard: Direct Manpower, Project Allowance, Travel &amp; Accommodations, Vehicle Leasing / Cost, Equipment &amp; Hardware, Permit &amp; Regulatory, Other Direct Project Cost, Salary, Shared Service.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Boleh tambah Subcategory baru kalau perlu — app akan terima category/subcategory baru secara automatik.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. MONTH ADALAH WAJIB — PROFIT perlukan bulan pada SETIAP baris data untuk Grid view, Forecast, dan laporan trend bulanan berfungsi. Data tanpa bulan akan DITOLAK semasa upload.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. JANGAN merge cell pada column Type/Category — taip value pada SETIAP baris walaupun berulang.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7. Isi angka bulanan sahaja — column Total auto-kira, jangan edit terus.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8. Untuk expense/Cash-Out, taip nombor POSITIF — app auto-tolak (negative) bila import berdasarkan Type.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9. Header bulan dah label dengan tahun 2026 (cth: Jan-26). Tukar terus tajuk column kalau data untuk tahun lain.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10. Padam baris contoh (bergaris hijau) sebelum isi data sebenar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bila upload dalam app, pilih statement type (PnL/Cashflow) yang sepadan dengan tab yang diisi.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PnL Template (Monthly) — isi bermula dari baris 5. JANGAN merge cell, JANGAN tukar nama header (Type, Category, Total).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type = 'Revenue' atau 'Expenses' — TAIP pada SETIAP baris (jangan biarkan kosong). Category = item spesifik (contoh: Direct Manpower). Bulan (WAJIB) sudah label dengan tahun 2026 — tukar tajuk column kalau nak tahun lain.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isi angka bulanan (column C-N). Column 'Total' auto-kira (formula). Untuk Expenses/expense, taip nombor POSITIF sahaja — app auto-tolak (jadi negatif) secara automatik ikut Type.</t>
+    <t xml:space="preserve">How to use this template</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. There are 2 tabs: 'PnL' and 'Cashflow'. Fill in the relevant tab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. The Category/Type and Subcategory names in this template match exactly what PROFIT uses — do not rename them, so data is sorted correctly automatically.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Standard cost Subcategory list: Direct Manpower, Project Allowance, Travel &amp; Accommodations, Vehicle Leasing / Cost, Equipment &amp; Hardware, Permit &amp; Regulatory, Other Direct Project Cost, Salary, Shared Service.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. You can add new Subcategories if needed — the app will accept new category/subcategory names automatically.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. MONTH IS REQUIRED — PROFIT needs a month on every row of data for Grid view, Forecast, and monthly trend reporting to work. Data without a month will be REJECTED on upload.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. DO NOT merge cells in the Type/Category columns — type the value on EVERY row even if it repeats.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. Fill in monthly figures only — the Total column auto-calculates, do not edit it directly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. For expenses/Cash-Out, type POSITIVE numbers — the app auto-flips the sign (negative) on import based on Type.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. Month headers are already labeled with year 2026 (e.g. Jan-26). Edit the column headers directly if you need a different year.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10. Delete the example rows (highlighted green) before entering real data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When uploading in the app, select the statement type (PnL/Cashflow) that matches the tab you filled in.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PnL Template (Monthly) — start filling from row 5. DO NOT merge cells, DO NOT rename headers (Type, Category, Total).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type = 'Revenue' or 'Expenses' — TYPE it on EVERY row (do not leave blank even if same as row above). Category = specific item (e.g. Direct Manpower).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fill in monthly figures (columns C-N). The 'Total' column auto-calculates (formula). For Expenses/expenses, type POSITIVE numbers only — the app automatically flips the sign based on Type.</t>
   </si>
   <si>
     <t xml:space="preserve">Type</t>
@@ -150,13 +150,13 @@
     <t xml:space="preserve">Shared Service</t>
   </si>
   <si>
-    <t xml:space="preserve">Cashflow Template (Monthly) — isi bermula dari baris 5. JANGAN merge cell, JANGAN tukar nama header (Type, Category, Total).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type = 'Cash-In' atau 'Cash-Out' — TAIP pada SETIAP baris (jangan biarkan kosong). Category = item spesifik (contoh: Direct Manpower). Bulan (WAJIB) sudah label dengan tahun 2026 — tukar tajuk column kalau nak tahun lain.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isi angka bulanan (column C-N). Column 'Total' auto-kira (formula). Untuk Cash-Out/expense, taip nombor POSITIF sahaja — app auto-tolak (jadi negatif) secara automatik ikut Type.</t>
+    <t xml:space="preserve">Cashflow Template (Monthly) — start filling from row 5. DO NOT merge cells, DO NOT rename headers (Type, Category, Total).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type = 'Cash-In' or 'Cash-Out' — TYPE it on EVERY row (do not leave blank even if same as row above). Category = specific item (e.g. Direct Manpower).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fill in monthly figures (columns C-N). The 'Total' column auto-calculates (formula). For Cash-Out/expenses, type POSITIVE numbers only — the app automatically flips the sign based on Type.</t>
   </si>
   <si>
     <t xml:space="preserve">Cash-In</t>
@@ -706,7 +706,7 @@
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
